--- a/mapping/SB_DWH/Mapping_FCT_RLOS_CUSTOMER.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_CUSTOMER.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +718,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -735,7 +746,6 @@
           <t>NG_SB_RLOS_APPLICANT_IDGRID AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -753,7 +763,6 @@
           <t>DIM_RLOS_APPLICATION AS B</t>
         </is>
       </c>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -771,7 +780,6 @@
           <t>NG_SB_RLOS_APPLICANT_GENERAL AS C</t>
         </is>
       </c>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -789,7 +797,6 @@
           <t>NG_SB_RLOS_APPLICANT_DETAIL AS D</t>
         </is>
       </c>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -798,7 +805,6 @@
           <t>NG_SB_RLOS_MAS_CITY AS E</t>
         </is>
       </c>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -807,47 +813,38 @@
           <t>NG_SB_RLOS_MAS_DISTRICT AS F</t>
         </is>
       </c>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -875,9 +872,8 @@
           <t>How to mapping RLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -891,9 +887,8 @@
           <t>ROW_NUMBER() OVER (PARTITION BY A.WI_NAME, A.ID_TYPE, A.ID_NUMBER ORDER BY A.RECID DESC) = 1</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -909,19 +904,18 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK — Driving: NG_SB_RLOS_APPLICANT_IDGRID. Ngày dữ liệu, dạng số YYYYMMDD. Snapshot hàng ngày — mỗi ngày lặp lại toàn bộ giấy tờ của mọi hồ sơ đang active, giống pattern FCT_RLOS_APPLICATION. T24_CUSTOMER_SK không còn ở SB_DWH — việc tính chuyển hẳn xuống PDTD_DTM.FCT_RLOS_CUSTOMER (nơi STG_DIM_CUSTOMER đã có sẵn cùng tầng)</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>CUSTOMER_BK</t>
@@ -937,19 +931,18 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ hash của tổ hợp (hồ sơ, loại giấy tờ, số giấy tờ). Cùng công thức/mục đích với EXCEPTION_BK (DIM_CLOS_EXCEPTION/DIM_RLOS_EXCEPTION)</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>STANDARD_HASH(A.WI_NAME || A.ID_TYPE || A.ID_NUMBER, 'MD5')</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -965,19 +958,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_RLOS_APPLICATION, join theo WI_NAME + điều kiện SCD2 hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại — tra DIM_RLOS_APPLICATION, join theo WI_NAME + điều kiện SCD2 hiệu lực tại DAYID</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>B.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>WI_NAME</t>
@@ -993,19 +985,18 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ RLOS. Quan hệ 1:N với giấy tờ (1 hồ sơ có thể có nhiều giấy tờ)</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
           <t>ID_TYPE</t>
@@ -1021,17 +1012,16 @@
           <t>Loại giấy tờ định danh</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
         <is>
           <t>Loại giấy tờ định danh. 14 giá trị quan sát được (BLX, CMND, CMNDQD, DKKD...); SRS BC1 dùng nhóm TCC/CC làm khóa lọc ADD_ID</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>A.ID_TYPE</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -1049,17 +1039,16 @@
           <t>Số giấy tờ định danh</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Số giấy tờ định danh</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.ID_NUMBER</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -1077,17 +1066,16 @@
           <t>Ngày cấp giấy tờ</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Ngày cấp giấy tờ. Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.ISSUE_DATE</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1105,17 +1093,16 @@
           <t>Ngày hết hạn giấy tờ</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Ngày hết hạn giấy tờ. Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.EXPIRY_DATE</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
@@ -1133,17 +1120,16 @@
           <t>Nơi cấp giấy tờ</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Nơi cấp giấy tờ. Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.ISSUE_PLACE</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1161,17 +1147,16 @@
           <t>Ngày cấp visa</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Ngày cấp visa (khách hàng nước ngoài). Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.ISSUE_DATE_VISA</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -1189,19 +1174,18 @@
           <t>Ngày hết hạn visa</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Ngày hết hạn visa (khách hàng nước ngoài). Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>A.EXPIRY_DATE_VISA</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
           <t>CUST_CLASS</t>
@@ -1217,17 +1201,16 @@
           <t>Phân loại khách hàng theo giấy tờ</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Phân loại khách hàng theo giấy tờ (CLASS.IND.UNDEFINED/CLASS.MASS/CLASS.SB.STAFF/CLASS.VIPS). Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.CUST_CLASS</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
@@ -1245,19 +1228,18 @@
           <t>Cờ tự động lấy từ hệ định danh</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Cờ giấy tờ có được tự động lấy từ hệ định danh hay không. Thiết kế dư thừa</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.IS_FETCH</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>CIF</t>
@@ -1273,17 +1255,16 @@
           <t>Mã CIF khách hàng</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Mã CIF khách hàng, nếu đã định danh. Hiện chưa có report nào dùng trực tiếp (SRS BC1 dùng T24_CUSTOMER_SK làm chân T24 chính thức), giữ dạng dư thừa vì có ý nghĩa nghiệp vụ thật</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>A.CIF</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
@@ -1301,17 +1282,16 @@
           <t>Họ tên đầy đủ</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Họ tên đầy đủ</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>C.FULL_NAME</t>
         </is>
       </c>
-      <c r="F31" s="28" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
@@ -1329,17 +1309,16 @@
           <t>Ngày sinh</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Ngày sinh</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>C.DOB</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
@@ -1357,17 +1336,16 @@
           <t>Giới tính</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Giới tính</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>C.GENDER</t>
         </is>
       </c>
-      <c r="F33" s="28" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
@@ -1385,17 +1363,16 @@
           <t>Quốc tịch</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Quốc tịch (mã)</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>C.NATIONALITY</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
@@ -1413,17 +1390,16 @@
           <t>Danh xưng</t>
         </is>
       </c>
-      <c r="D35" s="27" t="inlineStr">
+      <c r="D35" s="54" t="inlineStr">
         <is>
           <t>Danh xưng</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>C.TITLE</t>
         </is>
       </c>
-      <c r="F35" s="28" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
@@ -1441,17 +1417,16 @@
           <t>SĐT nhà riêng</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>Số điện thoại nhà riêng</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>C.HOME_PHONE</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="28" t="inlineStr">
@@ -1469,17 +1444,16 @@
           <t>SĐT di động chính</t>
         </is>
       </c>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>Số điện thoại di động chính</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>C.PHONE_1</t>
         </is>
       </c>
-      <c r="F37" s="28" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="28" t="inlineStr">
@@ -1497,17 +1471,16 @@
           <t>SĐT phụ</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="D38" s="54" t="inlineStr">
         <is>
           <t>Số điện thoại phụ</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>C.PHONE2</t>
         </is>
       </c>
-      <c r="F38" s="28" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="28" t="inlineStr">
@@ -1525,17 +1498,16 @@
           <t>Tình trạng hôn nhân</t>
         </is>
       </c>
-      <c r="D39" s="27" t="inlineStr">
+      <c r="D39" s="54" t="inlineStr">
         <is>
           <t>Tình trạng hôn nhân</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>D.MARR_STATUS</t>
         </is>
       </c>
-      <c r="F39" s="28" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="28" t="inlineStr">
@@ -1553,17 +1525,16 @@
           <t>Trình độ học vấn</t>
         </is>
       </c>
-      <c r="D40" s="27" t="inlineStr">
+      <c r="D40" s="54" t="inlineStr">
         <is>
           <t>Trình độ học vấn</t>
         </is>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>D.EDU_LEVEL</t>
         </is>
       </c>
-      <c r="F40" s="28" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="28" t="inlineStr">
@@ -1581,17 +1552,16 @@
           <t>Phương tiện đi lại</t>
         </is>
       </c>
-      <c r="D41" s="27" t="inlineStr">
+      <c r="D41" s="54" t="inlineStr">
         <is>
           <t>Phương tiện đi lại</t>
         </is>
       </c>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>D.VEHICLE</t>
         </is>
       </c>
-      <c r="F41" s="28" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="28" t="inlineStr">
@@ -1609,17 +1579,16 @@
           <t>Địa chỉ thường trú</t>
         </is>
       </c>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="D42" s="54" t="inlineStr">
         <is>
           <t>Địa chỉ thường trú</t>
         </is>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E42" s="31" t="inlineStr">
         <is>
           <t>D.PERM_ADD</t>
         </is>
       </c>
-      <c r="F42" s="28" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="28" t="inlineStr">
@@ -1637,17 +1606,16 @@
           <t>Số nhà hiện tại</t>
         </is>
       </c>
-      <c r="D43" s="27" t="inlineStr">
+      <c r="D43" s="54" t="inlineStr">
         <is>
           <t>Số nhà thuộc địa chỉ hiện tại</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>D.HOUSNO_CURR_RES</t>
         </is>
       </c>
-      <c r="F43" s="28" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="28" t="inlineStr">
@@ -1665,17 +1633,16 @@
           <t>Phường xã hiện tại</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="D44" s="54" t="inlineStr">
         <is>
           <t>Phường xã thuộc địa chỉ hiện tại</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E44" s="31" t="inlineStr">
         <is>
           <t>D.WARD_CURR_RES</t>
         </is>
       </c>
-      <c r="F44" s="28" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="28" t="inlineStr">
@@ -1693,17 +1660,16 @@
           <t>Mã tỉnh/thành phố</t>
         </is>
       </c>
-      <c r="D45" s="27" t="inlineStr">
+      <c r="D45" s="54" t="inlineStr">
         <is>
           <t>Mã tỉnh/thành phố thuộc địa chỉ hiện tại</t>
         </is>
       </c>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>E.CITY_CODE</t>
         </is>
       </c>
-      <c r="F45" s="28" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="28" t="inlineStr">
@@ -1721,17 +1687,16 @@
           <t>Tên tỉnh/thành phố</t>
         </is>
       </c>
-      <c r="D46" s="27" t="inlineStr">
+      <c r="D46" s="54" t="inlineStr">
         <is>
           <t>Tên tỉnh/thành phố</t>
         </is>
       </c>
-      <c r="E46" s="28" t="inlineStr">
+      <c r="E46" s="31" t="inlineStr">
         <is>
           <t>E.CITY_NAME</t>
         </is>
       </c>
-      <c r="F46" s="28" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="28" t="inlineStr">
@@ -1749,17 +1714,16 @@
           <t>Tên tỉnh/thành phố (tiếng Việt)</t>
         </is>
       </c>
-      <c r="D47" s="27" t="inlineStr">
+      <c r="D47" s="54" t="inlineStr">
         <is>
           <t>Tên tỉnh/thành phố tiếng Việt có dấu</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>E.CITY_NAME_VN</t>
         </is>
       </c>
-      <c r="F47" s="28" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="28" t="inlineStr">
@@ -1777,17 +1741,16 @@
           <t>Mã quận/huyện</t>
         </is>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="D48" s="54" t="inlineStr">
         <is>
           <t>Mã quận/huyện thuộc địa chỉ hiện tại</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E48" s="31" t="inlineStr">
         <is>
           <t>F.DISTRICT_CODE</t>
         </is>
       </c>
-      <c r="F48" s="28" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="28" t="inlineStr">
@@ -1805,19 +1768,18 @@
           <t>Tên quận/huyện</t>
         </is>
       </c>
-      <c r="D49" s="27" t="inlineStr">
+      <c r="D49" s="54" t="inlineStr">
         <is>
           <t>Tên quận/huyện</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>F.DISTRICT_NAME</t>
         </is>
       </c>
-      <c r="F49" s="28" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+    </row>
+    <row r="50" ht="45" customHeight="1">
       <c r="A50" s="28" t="inlineStr">
         <is>
           <t>DISTRICT_NAME_VN</t>
@@ -1833,19 +1795,18 @@
           <t>Tên quận/huyện (tiếng Việt)</t>
         </is>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="D50" s="54" t="inlineStr">
         <is>
           <t>Tên quận/huyện tiếng Việt có dấu. PHÁI SINH: lấy DISTRICT_NAME_VN nhưng gán NULL với giá trị lỗi '#NA'/'#REF!' còn sót từ khâu import Excel</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E50" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN F.DISTRICT_NAME_VN IN ('#NA','#REF!') THEN NULL ELSE F.DISTRICT_NAME_VN END</t>
         </is>
       </c>
-      <c r="F50" s="28" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
+    </row>
+    <row r="51" ht="45" customHeight="1">
       <c r="A51" s="28" t="inlineStr">
         <is>
           <t>CUS_SEGMENT</t>
@@ -1861,189 +1822,83 @@
           <t>Phân khúc khách hàng (LOS)</t>
         </is>
       </c>
-      <c r="D51" s="27" t="inlineStr">
+      <c r="D51" s="54" t="inlineStr">
         <is>
           <t>Phân khúc khách hàng theo LOS (giá trị gốc, chưa chuẩn hóa). CUSTOMER_SEGMENT (chuẩn hóa CASE WHEN) chuyển hẳn sang tính tại PDTD_DTM, không có ở SB_DWH</t>
         </is>
       </c>
-      <c r="E51" s="28" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>D.CUS_SEGMENT</t>
         </is>
       </c>
-      <c r="F51" s="28" t="n"/>
-    </row>
-    <row r="52" ht="34" customHeight="1"/>
+    </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="10" t="n"/>
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
-      <c r="D53" s="54" t="inlineStr">
+      <c r="D53" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-    </row>
-    <row r="54" ht="45" customHeight="1">
+    </row>
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="25" t="n"/>
       <c r="B54" s="25" t="n"/>
       <c r="C54" s="51" t="n"/>
-      <c r="D54" s="8" t="n"/>
+      <c r="D54" s="54" t="n"/>
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="25" t="n"/>
       <c r="B55" s="25" t="n"/>
       <c r="C55" s="51" t="n"/>
-      <c r="D55" s="8" t="n"/>
+      <c r="D55" s="54" t="n"/>
       <c r="E55" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN C.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="25" t="n"/>
       <c r="B56" s="25" t="n"/>
       <c r="C56" s="51" t="n"/>
-      <c r="D56" s="8" t="n"/>
+      <c r="D56" s="54" t="n"/>
       <c r="E56" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN D.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="25" t="n"/>
       <c r="B57" s="25" t="n"/>
       <c r="C57" s="51" t="n"/>
-      <c r="D57" s="8" t="n"/>
+      <c r="D57" s="54" t="n"/>
       <c r="E57" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN E.CITY_CODE = D.CITY_CURR_RES</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
+    </row>
+    <row r="58" ht="15" customHeight="1">
       <c r="A58" s="25" t="n"/>
       <c r="B58" s="25" t="n"/>
       <c r="C58" s="51" t="n"/>
-      <c r="D58" s="8" t="n"/>
+      <c r="D58" s="54" t="n"/>
       <c r="E58" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN F.DISTRICT_CODE = D.DISTRICT_CURR_RES</t>
         </is>
       </c>
-      <c r="F58" s="8" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
